--- a/test-robustness.xlsx
+++ b/test-robustness.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11003"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB232402-5E0C-47EF-85ED-7F6B102C116A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B816B3C9-735F-AE45-A6F3-530AF6C73116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1545" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9880" yWindow="500" windowWidth="18920" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,15 +15,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="36">
   <si>
     <t>test file</t>
   </si>
@@ -55,27 +52,15 @@
     <t>ddlk_3Txs.txt</t>
   </si>
   <si>
-    <t>aborts T2 correctly</t>
-  </si>
-  <si>
     <t>disj_multi_accesses.txt</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
-    <t>1000  OK</t>
-  </si>
-  <si>
     <t>no_conflict_2Txs.txt</t>
   </si>
   <si>
-    <t>1000 ok</t>
-  </si>
-  <si>
-    <t>hangs (as it should be)</t>
-  </si>
-  <si>
     <t>unlikely_ddlk.txt</t>
   </si>
   <si>
@@ -88,12 +73,6 @@
     <t>1000  ok</t>
   </si>
   <si>
-    <t>had to stop and continue</t>
-  </si>
-  <si>
-    <t>works</t>
-  </si>
-  <si>
     <t>(Feel free to create and test your own files, but include them as well)</t>
   </si>
   <si>
@@ -113,6 +92,42 @@
   </si>
   <si>
     <t>I encourage you to test at least 50000 times using tmtest for rrobustness!</t>
+  </si>
+  <si>
+    <t>Multiple aborts</t>
+  </si>
+  <si>
+    <t>Completed normally</t>
+  </si>
+  <si>
+    <t>Segmentation fault</t>
+  </si>
+  <si>
+    <t>NoC2T.txt</t>
+  </si>
+  <si>
+    <t>Transactions completed</t>
+  </si>
+  <si>
+    <t>Deadlock unresolved</t>
+  </si>
+  <si>
+    <t>Finished with deadlock abort</t>
+  </si>
+  <si>
+    <t>Deadlock detection works, but waiter tracking looks suspicious</t>
+  </si>
+  <si>
+    <t>Hangs</t>
+  </si>
+  <si>
+    <t>Segmentation fault and hangs</t>
+  </si>
+  <si>
+    <t>Did not open</t>
+  </si>
+  <si>
+    <t>only works for zgt_test</t>
   </si>
 </sst>
 </file>
@@ -172,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -187,16 +202,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,62 +490,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="3"/>
-    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="3"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="5"/>
+    <col min="4" max="4" width="12.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="7"/>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1"/>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-    </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
-        <v>23</v>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2"/>
+      <c r="B2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-    </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="1" t="s">
         <v>0</v>
@@ -541,36 +556,36 @@
         <v>7</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -578,19 +593,19 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>3</v>
       </c>
@@ -598,39 +613,39 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -638,10 +653,19 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F12" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -649,10 +673,19 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -660,19 +693,19 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="5">
-        <v>100</v>
+        <v>26</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -680,19 +713,19 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -700,56 +733,76 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
         <v>12</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>22</v>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
